--- a/data/burst speed/jess wheeler/sent from jess/raw/11.30.09 totals.xlsx
+++ b/data/burst speed/jess wheeler/sent from jess/raw/11.30.09 totals.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/wind-tunnel-flies/data/burst speed/jess wheeler/sent from jess/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D716DB90-F36E-7040-8B54-1243059700DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F6B152-B923-6E49-86C7-809BDACDA188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10580" yWindow="600" windowWidth="18060" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="206">
   <si>
     <t xml:space="preserve">Filename </t>
   </si>
@@ -650,6 +650,9 @@
   </si>
   <si>
     <t>n60m19.11.30.09-06</t>
+  </si>
+  <si>
+    <t>k45f19.11.30.09-04</t>
   </si>
 </sst>
 </file>
@@ -1036,7 +1039,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C616"/>
+  <dimension ref="A1:E616"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.6640625" customWidth="1"/>
@@ -3155,7 +3158,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="A193" s="1" t="s">
         <v>66</v>
       </c>
@@ -3166,9 +3169,9 @@
         <v>1.3440000000000001</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="A194" s="1" t="s">
-        <v>67</v>
+        <v>205</v>
       </c>
       <c r="B194" s="2">
         <v>111.801</v>
@@ -3176,10 +3179,13 @@
       <c r="C194" s="2">
         <v>0.84499999999999997</v>
       </c>
-    </row>
-    <row r="195" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+      <c r="E194" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="A195" s="1" t="s">
-        <v>67</v>
+        <v>205</v>
       </c>
       <c r="B195" s="2">
         <v>101.634</v>
@@ -3187,10 +3193,13 @@
       <c r="C195" s="2">
         <v>1.361</v>
       </c>
-    </row>
-    <row r="196" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+      <c r="E195" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="A196" s="1" t="s">
-        <v>67</v>
+        <v>205</v>
       </c>
       <c r="B196" s="2">
         <v>120.964</v>
@@ -3198,8 +3207,11 @@
       <c r="C196" s="2">
         <v>0.47399999999999998</v>
       </c>
-    </row>
-    <row r="197" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+      <c r="E196" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="A197" s="1" t="s">
         <v>68</v>
       </c>
@@ -3210,7 +3222,7 @@
         <v>0.89500000000000002</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="A198" s="1" t="s">
         <v>68</v>
       </c>
@@ -3221,7 +3233,7 @@
         <v>0.51300000000000001</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="A199" s="1" t="s">
         <v>68</v>
       </c>
@@ -3232,7 +3244,7 @@
         <v>1.972</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="A200" s="1" t="s">
         <v>69</v>
       </c>
@@ -3243,7 +3255,7 @@
         <v>1.143</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="A201" s="1" t="s">
         <v>69</v>
       </c>
@@ -3254,7 +3266,7 @@
         <v>0.55800000000000005</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="A202" s="1" t="s">
         <v>69</v>
       </c>
@@ -3265,7 +3277,7 @@
         <v>0.57399999999999995</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="A203" s="1" t="s">
         <v>70</v>
       </c>
@@ -3276,7 +3288,7 @@
         <v>1.978</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="A204" s="1" t="s">
         <v>70</v>
       </c>
@@ -3287,7 +3299,7 @@
         <v>0.95799999999999996</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="A205" s="1" t="s">
         <v>70</v>
       </c>
@@ -3298,7 +3310,7 @@
         <v>0.89800000000000002</v>
       </c>
     </row>
-    <row r="206" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="A206" s="1" t="s">
         <v>71</v>
       </c>
@@ -3309,7 +3321,7 @@
         <v>1.9350000000000001</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="A207" s="1" t="s">
         <v>71</v>
       </c>
@@ -3320,7 +3332,7 @@
         <v>1.1060000000000001</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="A208" s="1" t="s">
         <v>71</v>
       </c>
